--- a/report_forms/016_escalation_interaction_log--report_forms.xlsx
+++ b/report_forms/016_escalation_interaction_log--report_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -734,8 +734,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
-    <col width="37" customWidth="1" min="2" max="2"/>
-    <col width="37" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -763,12 +763,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'phone'}</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Phone'}</t>
+          <t>Phone</t>
         </is>
       </c>
     </row>
@@ -780,12 +780,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'email'}</t>
+          <t>email</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Email'}</t>
+          <t>Email</t>
         </is>
       </c>
     </row>
@@ -797,12 +797,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'none'}</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'None'}</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -814,12 +814,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'chat'}</t>
+          <t>chat</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'Chat'}</t>
+          <t>Chat</t>
         </is>
       </c>
     </row>
@@ -831,12 +831,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_5,_'name':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 5, 'name': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -848,12 +848,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'resolved'}</t>
+          <t>resolved</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Resolved'}</t>
+          <t>Resolved</t>
         </is>
       </c>
     </row>
@@ -865,12 +865,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'pending'}</t>
+          <t>pending</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Pending'}</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
@@ -882,12 +882,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'closed'}</t>
+          <t>closed</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Closed'}</t>
+          <t>Closed</t>
         </is>
       </c>
     </row>
@@ -899,12 +899,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'not_applicable'}</t>
+          <t>not_applicable</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'Not Applicable'}</t>
+          <t>Not Applicable</t>
         </is>
       </c>
     </row>
